--- a/data_produksi/bms/bms.xlsx
+++ b/data_produksi/bms/bms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Tanggal</t>
   </si>
@@ -116,6 +116,48 @@
   </si>
   <si>
     <t>3613EA20250425070001</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1201CA230626040001</t>
+  </si>
+  <si>
+    <t>1201CA230626040002</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1201CA220526040003</t>
+  </si>
+  <si>
+    <t>1201CA220526040004</t>
+  </si>
+  <si>
+    <t>1201CA220426040005</t>
+  </si>
+  <si>
+    <t>1201CA220426040006</t>
+  </si>
+  <si>
+    <t>1201CA220426040007</t>
+  </si>
+  <si>
+    <t>1201CA240426040008</t>
+  </si>
+  <si>
+    <t>1201CA220426040009</t>
+  </si>
+  <si>
+    <t>1201CA220426040010</t>
+  </si>
+  <si>
+    <t>1201CA220426040012</t>
+  </si>
+  <si>
+    <t>1201CA220426040013</t>
   </si>
 </sst>
 </file>
@@ -655,6 +697,138 @@
         <v>16</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data_produksi/bms/bms.xlsx
+++ b/data_produksi/bms/bms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Tanggal</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>1201CA220426040013</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>1201CA260526050023</t>
   </si>
 </sst>
 </file>
@@ -829,6 +835,17 @@
         <v>16</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>